--- a/05_Figures/F06_prediction/proteins/T2/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T2/d_fcsa_I/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -140,402 +140,387 @@
     <t xml:space="preserve">AIMP2</t>
   </si>
   <si>
+    <t xml:space="preserve">MLEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBB2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">CACNG1</t>
   </si>
   <si>
-    <t xml:space="preserve">MLEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBB2A</t>
-  </si>
-  <si>
     <t xml:space="preserve">DCTN2</t>
   </si>
   <si>
+    <t xml:space="preserve">FSCN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDI2</t>
+  </si>
+  <si>
     <t xml:space="preserve">NDUFAB1</t>
   </si>
   <si>
-    <t xml:space="preserve">FSCN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDI2</t>
-  </si>
-  <si>
     <t xml:space="preserve">SLC44A2</t>
   </si>
   <si>
     <t xml:space="preserve">CAMK2A</t>
   </si>
   <si>
+    <t xml:space="preserve">EIF5B</t>
+  </si>
+  <si>
     <t xml:space="preserve">HADHA</t>
   </si>
   <si>
+    <t xml:space="preserve">MAP2K2</t>
+  </si>
+  <si>
     <t xml:space="preserve">MYBPC2</t>
   </si>
   <si>
     <t xml:space="preserve">ASPH</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF5B</t>
-  </si>
-  <si>
     <t xml:space="preserve">LACTB</t>
   </si>
   <si>
-    <t xml:space="preserve">MAP2K2</t>
+    <t xml:space="preserve">CRIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
   </si>
   <si>
     <t xml:space="preserve">MAPK1</t>
   </si>
   <si>
-    <t xml:space="preserve">DUSP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
-  </si>
-  <si>
     <t xml:space="preserve">MB</t>
   </si>
   <si>
+    <t xml:space="preserve">PFDN2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PHKG1</t>
   </si>
   <si>
     <t xml:space="preserve">RPL17</t>
   </si>
   <si>
+    <t xml:space="preserve">RPL23A</t>
+  </si>
+  <si>
     <t xml:space="preserve">SUMO2</t>
   </si>
   <si>
+    <t xml:space="preserve">ERGIC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGLY1</t>
+  </si>
+  <si>
     <t xml:space="preserve">UBE2M</t>
   </si>
   <si>
+    <t xml:space="preserve">XRCC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB11B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYPL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA2G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCYL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BZW2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAP1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YWHAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOBEC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGDIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSD17B12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDRG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCBP2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PDIA4</t>
   </si>
   <si>
-    <t xml:space="preserve">PFDN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL23A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XRCC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERGIC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGLY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB11B</t>
+    <t xml:space="preserve">RPL4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNJ2BP</t>
   </si>
   <si>
     <t xml:space="preserve">TNPO3</t>
   </si>
   <si>
-    <t xml:space="preserve">CRIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA2G4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYPL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENDOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BZW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDRG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAP1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCYL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGDIB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7B</t>
+    <t xml:space="preserve">TTC38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UFL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH16A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APMAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNA1S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYB5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDAH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPP3</t>
   </si>
   <si>
     <t xml:space="preserve">EHD4</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF3L</t>
+    <t xml:space="preserve">ESYT1</t>
   </si>
   <si>
     <t xml:space="preserve">HECTD1</t>
   </si>
   <si>
-    <t xml:space="preserve">HSD17B12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCBP2</t>
+    <t xml:space="preserve">HK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYL4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NME2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUDT16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABPC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD6IP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLDIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP5C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAR2A</t>
   </si>
   <si>
     <t xml:space="preserve">PSMB2</t>
   </si>
   <si>
-    <t xml:space="preserve">RPL4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNJ2BP</t>
+    <t xml:space="preserve">RAB8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCARB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTBN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STK38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAGLN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
   </si>
   <si>
     <t xml:space="preserve">TSPO</t>
   </si>
   <si>
-    <t xml:space="preserve">TXN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UFL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YWHAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH16A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APMAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOBEC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYB5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDAH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPM2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERP29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIF5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANCL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METAP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYL4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABPC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLDIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP5C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAR2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBMX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCARB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTBN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STK38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGLN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
     <t xml:space="preserve">TXN</t>
   </si>
   <si>
@@ -543,9 +528,6 @@
   </si>
   <si>
     <t xml:space="preserve">WDR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YARS1</t>
   </si>
   <si>
     <t xml:space="preserve">YWHAH</t>
@@ -935,16 +917,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.544335715912535</v>
+        <v>-0.487412997343759</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.375</v>
+        <v>-0.292857142857143</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -968,29 +950,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.544335715912535</v>
+        <v>-0.487412997343759</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.427860696517413</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.671641791044776</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.683435965177877</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.680083784898559</v>
-      </c>
+        <v>-0.292857142857143</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1014,2206 +988,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.76852467051142</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.134664733978405</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.811169994132726</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.19261096067588</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.444890774236027</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.913879589964826</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0227921026339821</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.849991132740502</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.70301196834608</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.67834459896096</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.157367360580677</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.285388556345017</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.472223144508168</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.724783321789751</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.323915718749107</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-2.30817297081665</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.752837509159904</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.255349364767324</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.458592789146806</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.998562303989084</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.737076335231633</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.782463717060419</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.742014785651145</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.617178541601268</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.198170291198799</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-1.2666597147628</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.374563401502819</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-2.63529933427501</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-1.03636628280388</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.274792822382735</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-2.57927634709693</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.491453593781593</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.08089494294569</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.0979609937025676</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.248418905945171</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.829538659256933</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.267778521834454</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.541884989927769</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-3.9607185036416</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.624046245964834</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.744030372009794</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.04611615068326</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.756369293470478</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.775024030293619</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.56395164551789</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-2.87732755481787</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.54879389614943</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-1.53096969072108</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.566404531502639</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.201307847217359</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.75198691217851</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.0433540225211537</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.0381382262847261</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.820541702710936</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.19342145350239</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-1.78249474226724</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.0994031009118956</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.289480389927442</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.951325564110463</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-1.23535281652661</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.831111553836191</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.41761519143717</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.603994975647154</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.15569927795607</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.924750973858139</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.0895286891103286</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.351981230207007</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-1.16374858335451</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.100867874677691</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.53954503655168</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.896302224967078</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.902314774922192</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.38147496063975</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-1.88122677299423</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.81632859360847</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.357829381406662</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.173093694559983</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.572702578679508</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.842871652065619</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.272789566163701</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.150917127682463</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.657376015435909</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-1.37080179884859</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.0868925187739313</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.156872312016756</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.492882592755576</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.531222672658735</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.741835169000986</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.355026547797163</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.8611245057994</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0.0620956862940647</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-1.77851573259581</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.04281767556739</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.197157210930344</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.681697066058617</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.708380619341581</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.531556067706966</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.241704799053019</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-1.15586390662771</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.73994400707726</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.36291512962826</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.556865158594628</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.915758386121043</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.0476846797973789</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.0436998988028796</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.28929065770951</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.686054691272593</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.377218860113968</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.896878646216278</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-1.82350213368838</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.879443222146916</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.608802077712464</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.0133497668395643</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-1.06768421568435</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.224039306505144</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.594863576798401</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.247314547735374</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.698914841591948</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.80622582321433</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-1.53412938668848</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>0.32679726966347</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.19086346501271</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.825659055336565</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.505985121905098</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.239015951882209</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.167426005291731</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.975132974606579</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.352141654796018</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.523701328450374</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.945066877599233</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.457860407176512</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.940578633956767</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.461571961756819</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-1.01530277653875</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-1.67037181835616</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.356160791883614</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0.279259016739937</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.743772515467248</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.909233667712272</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.608418345868468</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.559419386285024</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.262650817775016</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.672353674196791</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.0860324574072264</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.66473287602402</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-1.0555542838732</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.8604940841709</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>0.319973930798299</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-2.86590281485396</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-1.03579798242623</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.337056945211478</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.55043456486059</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.467798050310981</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.858849504285161</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.426086082383078</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>0.723147324880763</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.969872028470249</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.566775556395758</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.426443150006065</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.514220245013284</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.331566177126903</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.182468967449365</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.650033094158182</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0.229413488100073</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-1.20908123908043</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.16717791573391</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.117052855673937</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.227229303035446</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.82452920382742</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>0.435985659200357</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.38896492149997</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-1.0754880197704</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.29959430587836</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.836578201407962</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.51580843750139</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.70576806093893</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.934487831116983</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.659247959363831</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-1.98842779527222</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.651713157622429</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>0.181391417000582</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-2.10603102243087</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.916527200398707</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.105555901639728</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-1.81386305190908</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.0319859481494575</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.748635301726701</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.765420175196185</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.145297425152443</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.44146992592733</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.14686847139085</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.0830938693149081</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>0.351528999634138</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.379409393794621</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.25878765118002</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.507233118161848</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.447125860914279</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.841719695366804</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.21330958814821</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.850377350922113</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3256,7 +1030,7 @@
         <v>874.31</v>
       </c>
       <c r="E2" t="n">
-        <v>-237.080883780945</v>
+        <v>-234.916972222882</v>
       </c>
     </row>
     <row r="3">
@@ -3273,7 +1047,7 @@
         <v>1757.71</v>
       </c>
       <c r="E3" t="n">
-        <v>-511.780677944124</v>
+        <v>-475.86989398184</v>
       </c>
     </row>
     <row r="4">
@@ -3290,7 +1064,7 @@
         <v>1924.77</v>
       </c>
       <c r="E4" t="n">
-        <v>-545.179715366701</v>
+        <v>-353.302900777041</v>
       </c>
     </row>
     <row r="5">
@@ -3307,7 +1081,7 @@
         <v>274.62</v>
       </c>
       <c r="E5" t="n">
-        <v>-445.50902590737</v>
+        <v>-486.63601773988</v>
       </c>
     </row>
     <row r="6">
@@ -3324,7 +1098,7 @@
         <v>545.54</v>
       </c>
       <c r="E6" t="n">
-        <v>-916.393814572878</v>
+        <v>-857.378983808848</v>
       </c>
     </row>
     <row r="7">
@@ -3341,7 +1115,7 @@
         <v>1276.8</v>
       </c>
       <c r="E7" t="n">
-        <v>-1279.38792414878</v>
+        <v>-1354.7032155187</v>
       </c>
     </row>
     <row r="8">
@@ -3358,7 +1132,7 @@
         <v>-73.1099999999997</v>
       </c>
       <c r="E8" t="n">
-        <v>-718.903025800178</v>
+        <v>-666.648032013109</v>
       </c>
     </row>
     <row r="9">
@@ -3375,7 +1149,7 @@
         <v>171.549999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1376.1046217615</v>
+        <v>1340.34119460914</v>
       </c>
     </row>
     <row r="10">
@@ -3392,7 +1166,7 @@
         <v>621.64</v>
       </c>
       <c r="E10" t="n">
-        <v>385.68006938577</v>
+        <v>1106.33506045525</v>
       </c>
     </row>
     <row r="11">
@@ -3409,7 +1183,7 @@
         <v>-1588.06</v>
       </c>
       <c r="E11" t="n">
-        <v>-125.088999032031</v>
+        <v>-194.286466833155</v>
       </c>
     </row>
     <row r="12">
@@ -3426,7 +1200,7 @@
         <v>-845.39</v>
       </c>
       <c r="E12" t="n">
-        <v>327.854249359548</v>
+        <v>448.685757370068</v>
       </c>
     </row>
     <row r="13">
@@ -3443,7 +1217,7 @@
         <v>-2646.36</v>
       </c>
       <c r="E13" t="n">
-        <v>113.640023780223</v>
+        <v>-81.9767092742141</v>
       </c>
     </row>
     <row r="14">
@@ -3460,7 +1234,7 @@
         <v>-1385.12</v>
       </c>
       <c r="E14" t="n">
-        <v>-1722.54356093149</v>
+        <v>-1638.08290289266</v>
       </c>
     </row>
     <row r="15">
@@ -3477,7 +1251,7 @@
         <v>-2594.04</v>
       </c>
       <c r="E15" t="n">
-        <v>587.980380784534</v>
+        <v>590.620168694093</v>
       </c>
     </row>
     <row r="16">
@@ -3494,7 +1268,7 @@
         <v>-1268.92</v>
       </c>
       <c r="E16" t="n">
-        <v>-173.223058582928</v>
+        <v>-156.205169559945</v>
       </c>
     </row>
   </sheetData>
@@ -3553,10 +1327,10 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0.933333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3570,10 +1344,10 @@
         <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -3621,10 +1395,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.866666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -3638,10 +1412,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3655,10 +1429,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3723,10 +1497,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
@@ -3740,10 +1514,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -3757,10 +1531,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -3808,10 +1582,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -3825,10 +1599,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -3842,10 +1616,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -3859,10 +1633,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="22">
@@ -3876,10 +1650,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -3893,10 +1667,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="24">
@@ -3910,10 +1684,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="25">
@@ -3927,10 +1701,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -3944,10 +1718,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -3961,10 +1735,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -4012,10 +1786,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31">
@@ -4029,10 +1803,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
@@ -4097,10 +1871,10 @@
         <v>71</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="36">
@@ -4114,10 +1888,10 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="37">
@@ -4131,10 +1905,10 @@
         <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -4148,10 +1922,10 @@
         <v>74</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -4165,10 +1939,10 @@
         <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="40">
@@ -4182,10 +1956,10 @@
         <v>76</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -4199,10 +1973,10 @@
         <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -4216,10 +1990,10 @@
         <v>78</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="43">
@@ -4233,10 +2007,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="44">
@@ -4403,10 +2177,10 @@
         <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -4420,10 +2194,10 @@
         <v>90</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="55">
@@ -4437,10 +2211,10 @@
         <v>91</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="56">
@@ -4454,10 +2228,10 @@
         <v>92</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="57">
@@ -4811,10 +2585,10 @@
         <v>113</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="78">
@@ -5800,108 +3574,6 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="s">
-        <v>172</v>
-      </c>
-      <c r="D136" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="s">
-        <v>173</v>
-      </c>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="s">
-        <v>174</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="s">
-        <v>175</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="s">
-        <v>176</v>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="s">
-        <v>177</v>
-      </c>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T2/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T2/d_fcsa_I/spls/c_data/results.xlsx
@@ -953,7 +953,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.487412997343759</v>
@@ -961,10 +961,18 @@
       <c r="I3" t="n">
         <v>-0.292857142857143</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.398009950248756</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.557213930348259</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.673278404474651</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.668540211985644</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -988,6 +996,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-2.22079311160997</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0902204966256385</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.46537047463472</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.718051833840394</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.43435891676601</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.886039173514765</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0715006983111127</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.820335893713868</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.734078788661602</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.71063690624336</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.180092370196365</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.273258700960781</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.238579556155076</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.762663290641311</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0633203867132458</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-2.61291359247425</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.668514533587712</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.260857374095553</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.0770620784993798</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.919381364584615</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.767590097486799</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.12469352621691</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.626794229254962</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.76366726875557</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.264935175512842</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.3697548090923</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.291047902689405</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-2.51111172893672</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.31211138948001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.23206567792947</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-2.26563131254754</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.159996504578047</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.15507645837887</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0635823998851826</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.36342804943718</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.704762835659131</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.462386700177837</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.199698147359743</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-3.88461755920354</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.681011664955861</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.590489529575557</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.980135286447986</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.842584984669026</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.782884425617131</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.2082260702861</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-2.46837354762083</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.71485870349899</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1.53347326203331</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.644888438487885</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.226173060080722</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.83994587460154</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0127621511285161</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0138243405166889</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.908432307109582</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-1.28841089194563</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.64796281590872</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.183550172001681</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.216738274783324</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.13338577999569</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.32915855382662</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.727478533185525</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.398025591405452</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.978325470319934</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.06363121557746</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.79608435453466</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.00235735391127978</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.281665324881379</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.02597064706663</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.0935976142696598</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.507835917630271</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.743599395873684</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.879127407903812</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.274555144913256</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-1.75669390679866</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.738361598942257</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.490730929262484</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.0263755191978692</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.324920162225242</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.975498854376801</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.275481149993783</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.179745923402247</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.625808185419405</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.41666092747089</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.00964304804308624</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.105714424526137</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.628455159326229</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.473436661886244</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.62281843653338</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.378969713979672</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.839352771545353</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.0626224936537646</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.42403537818891</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.03595309916716</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.253011619913185</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.528829980524786</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.880390968488264</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.640421012953168</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.211379039317395</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.14754157408826</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.729507311452615</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.32127559236147</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.801633588606427</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.06625938033518</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.0427350086348024</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.0803919054554085</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.380736417290267</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.62393923451161</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.198760231541834</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.86428959328098</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.77978486401661</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.814540795757298</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.845236904209185</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.0773341576635382</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.09471392155704</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.322355128014023</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.99004086181602</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.346158031941578</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.591611747662876</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.871110498445278</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.6208767045089</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.380947205920272</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.967894972776152</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.547051803405494</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.570514302169911</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.0608626596138244</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.241804778554521</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-1.01074671801145</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.234186768999267</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.456720254361901</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.11196320719579</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.441258929395343</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.03299585646919</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.812883536502431</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.10690856385924</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-1.8048342434359</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.441500247647138</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.139741820010431</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.825703965511465</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.887945715352356</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.525306023329844</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.539051631098779</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.119425465231421</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.969771651933495</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.224059846879568</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.54792169760059</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.11960815690941</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.975648677964707</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.327170216827082</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-2.58143568319189</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-1.1288221870569</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.355315062715131</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.611612265930541</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.295278466638466</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.929038428248842</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.351856454778848</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.71903005645768</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.950487030647736</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.623753462284038</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.330160111976958</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.527230207938009</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.167939682966193</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.100220119654766</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.670103660300664</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.242939862741271</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.20065514348845</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.928246561871757</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.129864595187837</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.23143438950864</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.72613145667252</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.443736505235303</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.20226025557853</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.14528679577068</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.02596822942118</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.826003398760408</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.51082415210438</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.750406012714755</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.0236510441337</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.733090289734441</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-1.78513422177686</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.57400802117586</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.0847318273379262</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.81956347412706</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.769128624378696</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.14248162447589</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.70072300883817</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.0330977123519491</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.785423881654431</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.689788804480015</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.0716312590829757</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.456125047923971</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.00932895593416005</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.0408578062433669</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.333683217623707</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.367977019183507</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1.19999058097905</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.528809665106884</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.250230707034782</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.794470184262897</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.32281764280104</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.502808954804955</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
